--- a/data/trans_orig/P33B_R3-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R3-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>93021</t>
+          <t>101457</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76406</t>
+          <t>85154</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113363</t>
+          <t>124131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>151598</t>
+          <t>167319</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>135921</t>
+          <t>150207</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169884</t>
+          <t>187295</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>268777</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>221114</t>
+          <t>243129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>271382</t>
+          <t>297749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>541391</t>
+          <t>588171</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>521049</t>
+          <t>565497</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>558006</t>
+          <t>604474</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>523772</t>
+          <t>565403</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>505486</t>
+          <t>545427</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>539449</t>
+          <t>582515</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1065163</t>
+          <t>1153573</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1038400</t>
+          <t>1124601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1088668</t>
+          <t>1179221</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,91%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1309782</t>
+          <t>1422350</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1309782</t>
+          <t>1422350</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1309782</t>
+          <t>1422350</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>146071</t>
+          <t>162930</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69966</t>
+          <t>139201</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>197086</t>
+          <t>193006</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>211555</t>
+          <t>236927</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>189135</t>
+          <t>213426</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>231843</t>
+          <t>262105</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>357626</t>
+          <t>399857</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>233567</t>
+          <t>367860</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>413417</t>
+          <t>433820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1045824</t>
+          <t>884999</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>994809</t>
+          <t>854923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1121929</t>
+          <t>908728</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>746551</t>
+          <t>833911</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>726263</t>
+          <t>808733</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>768971</t>
+          <t>857412</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1792376</t>
+          <t>1718910</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1736585</t>
+          <t>1684947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1916435</t>
+          <t>1750907</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>82,64%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191895</t>
+          <t>1047929</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191895</t>
+          <t>1047929</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191895</t>
+          <t>1047929</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150002</t>
+          <t>2118767</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150002</t>
+          <t>2118767</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150002</t>
+          <t>2118767</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>87515</t>
+          <t>96286</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69644</t>
+          <t>79397</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>107862</t>
+          <t>117760</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>132154</t>
+          <t>152499</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64283</t>
+          <t>133463</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>176388</t>
+          <t>172610</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>219669</t>
+          <t>248785</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145572</t>
+          <t>222967</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>261545</t>
+          <t>282064</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>617165</t>
+          <t>706787</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>596818</t>
+          <t>685313</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>635036</t>
+          <t>723676</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>801212</t>
+          <t>659760</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>756978</t>
+          <t>639649</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>869083</t>
+          <t>678796</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1418377</t>
+          <t>1366547</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1376501</t>
+          <t>1333268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1492474</t>
+          <t>1392365</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>86,2%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>173723</t>
+          <t>184760</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>150347</t>
+          <t>159009</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>200244</t>
+          <t>209795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>239190</t>
+          <t>265356</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>194949</t>
+          <t>241260</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>272926</t>
+          <t>288860</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>412914</t>
+          <t>450117</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>367525</t>
+          <t>416591</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>451074</t>
+          <t>484703</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>753108</t>
+          <t>805302</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>726587</t>
+          <t>780267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>776484</t>
+          <t>831053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>853403</t>
+          <t>852963</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>819667</t>
+          <t>829459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>897644</t>
+          <t>877059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1606510</t>
+          <t>1658264</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1568350</t>
+          <t>1623678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1651899</t>
+          <t>1691790</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>80,24%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>500330</t>
+          <t>545433</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>395284</t>
+          <t>502273</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>558367</t>
+          <t>593798</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>734497</t>
+          <t>822101</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>605619</t>
+          <t>778040</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>799633</t>
+          <t>864171</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1234827</t>
+          <t>1367535</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1074122</t>
+          <t>1309728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1331942</t>
+          <t>1428418</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2957488</t>
+          <t>2985259</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2899451</t>
+          <t>2936894</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3062534</t>
+          <t>3028419</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2924938</t>
+          <t>2912036</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2859802</t>
+          <t>2869966</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3053816</t>
+          <t>2956097</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5882426</t>
+          <t>5897295</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5785311</t>
+          <t>5836412</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6043131</t>
+          <t>5955102</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>81,97%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3457818</t>
+          <t>3530692</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7117253</t>
+          <t>7264830</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
